--- a/2022_04_29 PWC Challenge 1 - Hotel Analytics/output/top 3 by room type and month.xlsx
+++ b/2022_04_29 PWC Challenge 1 - Hotel Analytics/output/top 3 by room type and month.xlsx
@@ -1,40 +1,126 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seoul\Dropbox\00 technical\github\kimep-data-science-lab\2022_04_29 PWC Challenge 1 - Hotel Analytics\output\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1574BD-85CA-4341-A62C-ECE6780E1126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="20">
+  <si>
+    <t>Room type</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Concern description 1</t>
+  </si>
+  <si>
+    <t>Concern description 2</t>
+  </si>
+  <si>
+    <t>Concern description 3</t>
+  </si>
+  <si>
+    <t>Count_x 1</t>
+  </si>
+  <si>
+    <t>Count_x 2</t>
+  </si>
+  <si>
+    <t>Count_x 3</t>
+  </si>
+  <si>
+    <t>Club Deluxe King Room</t>
+  </si>
+  <si>
+    <t>Faulty electronics</t>
+  </si>
+  <si>
+    <t>Doesn’t match the website/brochure</t>
+  </si>
+  <si>
+    <t>Low-quality food</t>
+  </si>
+  <si>
+    <t>Executive Suite</t>
+  </si>
+  <si>
+    <t>Noisy neighbors</t>
+  </si>
+  <si>
+    <t>King Suite</t>
+  </si>
+  <si>
+    <t>Temperature of their room</t>
+  </si>
+  <si>
+    <t>Bad smells</t>
+  </si>
+  <si>
+    <t>One-Bedroom Club Room</t>
+  </si>
+  <si>
+    <t>One-Bedroom Suite</t>
+  </si>
+  <si>
+    <t>Superior King Room</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +128,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,14 +453,2046 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H217"/>
+  <sheetFormatPr defaultColWidth="20.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>7</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8">
+        <v>4</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10">
+        <v>7</v>
+      </c>
+      <c r="G10">
+        <v>4</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11">
+        <v>6</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14">
+        <v>6</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+      <c r="H14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15">
+        <v>7</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="H16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17">
+        <v>6</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="H17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18">
+        <v>7</v>
+      </c>
+      <c r="G18">
+        <v>6</v>
+      </c>
+      <c r="H18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20">
+        <v>6</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
+      <c r="H21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>3</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23">
+        <v>10</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23">
+        <v>4</v>
+      </c>
+      <c r="G23">
+        <v>4</v>
+      </c>
+      <c r="H23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24">
+        <v>11</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25">
+        <v>12</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26">
+        <v>4</v>
+      </c>
+      <c r="G26">
+        <v>17</v>
+      </c>
+      <c r="H26">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>13</v>
+      </c>
+      <c r="H27">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28">
+        <v>4</v>
+      </c>
+      <c r="G28">
+        <v>14</v>
+      </c>
+      <c r="H28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29">
+        <v>8</v>
+      </c>
+      <c r="H29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>3</v>
+      </c>
+      <c r="H30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <v>3</v>
+      </c>
+      <c r="H31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32">
+        <v>56</v>
+      </c>
+      <c r="G32">
+        <v>6</v>
+      </c>
+      <c r="H32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33">
+        <v>71</v>
+      </c>
+      <c r="G33">
+        <v>8</v>
+      </c>
+      <c r="H33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34">
+        <v>9</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34">
+        <v>97</v>
+      </c>
+      <c r="G34">
+        <v>8</v>
+      </c>
+      <c r="H34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35">
+        <v>10</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35">
+        <v>50</v>
+      </c>
+      <c r="G35">
+        <v>3</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36">
+        <v>11</v>
+      </c>
+      <c r="C36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36">
+        <v>52</v>
+      </c>
+      <c r="G36">
+        <v>5</v>
+      </c>
+      <c r="H36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37">
+        <v>12</v>
+      </c>
+      <c r="C37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37">
+        <v>54</v>
+      </c>
+      <c r="G37">
+        <v>5</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>6</v>
+      </c>
+      <c r="H38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="C39" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39">
+        <v>5</v>
+      </c>
+      <c r="G39">
+        <v>3</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40">
+        <v>3</v>
+      </c>
+      <c r="C40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>3</v>
+      </c>
+      <c r="H40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41">
+        <v>4</v>
+      </c>
+      <c r="C41" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41">
+        <v>2</v>
+      </c>
+      <c r="G41">
+        <v>2</v>
+      </c>
+      <c r="H41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>17</v>
+      </c>
+      <c r="B42">
+        <v>5</v>
+      </c>
+      <c r="C42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42">
+        <v>4</v>
+      </c>
+      <c r="G42">
+        <v>3</v>
+      </c>
+      <c r="H42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>17</v>
+      </c>
+      <c r="B43">
+        <v>6</v>
+      </c>
+      <c r="C43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44">
+        <v>6</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>17</v>
+      </c>
+      <c r="B45">
+        <v>8</v>
+      </c>
+      <c r="C45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45">
+        <v>5</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>17</v>
+      </c>
+      <c r="B46">
+        <v>9</v>
+      </c>
+      <c r="C46" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>17</v>
+      </c>
+      <c r="B47">
+        <v>10</v>
+      </c>
+      <c r="C47" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>2</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48">
+        <v>11</v>
+      </c>
+      <c r="C48" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" t="s">
+        <v>9</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>17</v>
+      </c>
+      <c r="B49">
+        <v>12</v>
+      </c>
+      <c r="C49" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" t="s">
+        <v>9</v>
+      </c>
+      <c r="F49">
+        <v>4</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50">
+        <v>6</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>18</v>
+      </c>
+      <c r="B51">
+        <v>2</v>
+      </c>
+      <c r="C51" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51">
+        <v>8</v>
+      </c>
+      <c r="G51">
+        <v>2</v>
+      </c>
+      <c r="H51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>18</v>
+      </c>
+      <c r="B52">
+        <v>3</v>
+      </c>
+      <c r="C52" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52">
+        <v>5</v>
+      </c>
+      <c r="G52">
+        <v>3</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>18</v>
+      </c>
+      <c r="B53">
+        <v>4</v>
+      </c>
+      <c r="C53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53">
+        <v>4</v>
+      </c>
+      <c r="G53">
+        <v>2</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>18</v>
+      </c>
+      <c r="B54">
+        <v>5</v>
+      </c>
+      <c r="C54" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54">
+        <v>7</v>
+      </c>
+      <c r="G54">
+        <v>6</v>
+      </c>
+      <c r="H54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>18</v>
+      </c>
+      <c r="B55">
+        <v>6</v>
+      </c>
+      <c r="C55" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" t="s">
+        <v>10</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>2</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>18</v>
+      </c>
+      <c r="B56">
+        <v>7</v>
+      </c>
+      <c r="C56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" t="s">
+        <v>10</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>18</v>
+      </c>
+      <c r="B57">
+        <v>8</v>
+      </c>
+      <c r="C57" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>4</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>18</v>
+      </c>
+      <c r="B58">
+        <v>9</v>
+      </c>
+      <c r="C58" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58">
+        <v>2</v>
+      </c>
+      <c r="H58">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B59">
+        <v>10</v>
+      </c>
+      <c r="C59" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>4</v>
+      </c>
+      <c r="H59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>18</v>
+      </c>
+      <c r="B60">
+        <v>11</v>
+      </c>
+      <c r="C60" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" t="s">
+        <v>10</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>3</v>
+      </c>
+      <c r="H60">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>18</v>
+      </c>
+      <c r="B61">
+        <v>12</v>
+      </c>
+      <c r="C61" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61" t="s">
+        <v>10</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>19</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62">
+        <v>16</v>
+      </c>
+      <c r="G62">
+        <v>23</v>
+      </c>
+      <c r="H62">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>19</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63" t="s">
+        <v>9</v>
+      </c>
+      <c r="F63">
+        <v>34</v>
+      </c>
+      <c r="G63">
+        <v>19</v>
+      </c>
+      <c r="H63">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>19</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" t="s">
+        <v>16</v>
+      </c>
+      <c r="E64" t="s">
+        <v>9</v>
+      </c>
+      <c r="F64">
+        <v>12</v>
+      </c>
+      <c r="G64">
+        <v>7</v>
+      </c>
+      <c r="H64">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>19</v>
+      </c>
+      <c r="B65">
+        <v>4</v>
+      </c>
+      <c r="C65" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" t="s">
+        <v>16</v>
+      </c>
+      <c r="E65" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65">
+        <v>28</v>
+      </c>
+      <c r="G65">
+        <v>11</v>
+      </c>
+      <c r="H65">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>19</v>
+      </c>
+      <c r="B66">
+        <v>5</v>
+      </c>
+      <c r="C66" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66">
+        <v>16</v>
+      </c>
+      <c r="G66">
+        <v>11</v>
+      </c>
+      <c r="H66">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>19</v>
+      </c>
+      <c r="B67">
+        <v>6</v>
+      </c>
+      <c r="C67" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" t="s">
+        <v>16</v>
+      </c>
+      <c r="E67" t="s">
+        <v>9</v>
+      </c>
+      <c r="F67">
+        <v>9</v>
+      </c>
+      <c r="G67">
+        <v>12</v>
+      </c>
+      <c r="H67">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>19</v>
+      </c>
+      <c r="B68">
+        <v>7</v>
+      </c>
+      <c r="C68" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" t="s">
+        <v>16</v>
+      </c>
+      <c r="E68" t="s">
+        <v>9</v>
+      </c>
+      <c r="F68">
+        <v>19</v>
+      </c>
+      <c r="G68">
+        <v>8</v>
+      </c>
+      <c r="H68">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>19</v>
+      </c>
+      <c r="B69">
+        <v>8</v>
+      </c>
+      <c r="C69" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" t="s">
+        <v>16</v>
+      </c>
+      <c r="E69" t="s">
+        <v>9</v>
+      </c>
+      <c r="F69">
+        <v>21</v>
+      </c>
+      <c r="G69">
+        <v>10</v>
+      </c>
+      <c r="H69">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>19</v>
+      </c>
+      <c r="B70">
+        <v>9</v>
+      </c>
+      <c r="C70" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" t="s">
+        <v>16</v>
+      </c>
+      <c r="E70" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70">
+        <v>5</v>
+      </c>
+      <c r="G70">
+        <v>11</v>
+      </c>
+      <c r="H70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>19</v>
+      </c>
+      <c r="B71">
+        <v>10</v>
+      </c>
+      <c r="C71" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" t="s">
+        <v>16</v>
+      </c>
+      <c r="E71" t="s">
+        <v>9</v>
+      </c>
+      <c r="F71">
+        <v>23</v>
+      </c>
+      <c r="G71">
+        <v>37</v>
+      </c>
+      <c r="H71">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>19</v>
+      </c>
+      <c r="B72">
+        <v>11</v>
+      </c>
+      <c r="C72" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72">
+        <v>6</v>
+      </c>
+      <c r="G72">
+        <v>5</v>
+      </c>
+      <c r="H72">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>19</v>
+      </c>
+      <c r="B73">
+        <v>12</v>
+      </c>
+      <c r="C73" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73" t="s">
+        <v>16</v>
+      </c>
+      <c r="E73" t="s">
+        <v>9</v>
+      </c>
+      <c r="F73">
+        <v>23</v>
+      </c>
+      <c r="G73">
+        <v>13</v>
+      </c>
+      <c r="H73">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="82" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="83" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="84" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="85" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="86" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="87" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="88" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="89" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="90" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="91" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="92" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="93" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="94" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="95" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="96" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="97" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="98" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="99" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="100" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="101" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="102" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="103" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="104" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="105" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="106" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="107" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="108" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="109" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="110" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="111" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="112" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="113" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="114" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="115" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="116" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="117" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="118" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="119" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="120" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="121" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="122" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="123" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="124" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="125" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="126" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="127" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="128" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="129" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="130" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="131" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="132" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="133" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="134" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="135" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="136" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="137" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="138" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="139" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="140" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="141" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="142" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="143" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="144" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="145" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="146" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="147" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="148" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="149" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="150" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="151" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="152" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="153" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="154" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="155" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="156" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="157" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="158" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="159" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="160" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="161" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="162" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="163" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="164" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="165" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="166" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="167" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="168" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="169" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="170" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="171" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="172" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="173" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="174" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="175" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="176" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="177" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="178" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="179" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="180" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="181" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="182" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="183" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="184" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="185" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="186" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="187" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="188" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="189" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="190" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="191" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="192" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="193" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="194" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="195" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="196" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="197" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="198" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="199" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="200" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="201" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="202" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="203" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="204" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="205" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="206" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="207" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="208" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="209" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="210" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="211" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="212" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="213" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="214" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="215" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="216" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="217" customFormat="1" x14ac:dyDescent="0.35"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>